--- a/data/CSMT_PNVL/dnhb_signals.xlsx
+++ b/data/CSMT_PNVL/dnhb_signals.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AB101"/>
+  <dimension ref="A1:AB103"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -2020,13 +2020,13 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>RVJ S-9</v>
+        <v>RVJ S-7</v>
       </c>
       <c r="B23" t="str">
         <v>VDLR</v>
       </c>
       <c r="C23" t="str">
-        <v>Wadala road</v>
+        <v>Wadala Road</v>
       </c>
       <c r="D23" t="str">
         <v>CSMT-PNVL</v>
@@ -2038,37 +2038,37 @@
         <v>DN</v>
       </c>
       <c r="G23" t="str">
-        <v>09/H142</v>
+        <v>VDLR PF-2</v>
       </c>
       <c r="H23" t="str">
-        <v>09/H142</v>
-      </c>
-      <c r="I23">
-        <v>9.636</v>
-      </c>
-      <c r="J23">
-        <v>19.02037</v>
-      </c>
-      <c r="K23">
-        <v>72.86103</v>
+        <v/>
+      </c>
+      <c r="I23" t="str">
+        <v/>
+      </c>
+      <c r="J23" t="str">
+        <v/>
+      </c>
+      <c r="K23" t="str">
+        <v/>
       </c>
       <c r="L23" t="str">
         <v>Semi-Automatic</v>
       </c>
       <c r="M23" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="N23" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23">
         <v>0</v>
       </c>
       <c r="Q23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -2077,22 +2077,22 @@
         <v>0</v>
       </c>
       <c r="T23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U23">
         <v>0</v>
       </c>
       <c r="V23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X23" t="str">
-        <v>RI: R1=PNVL</v>
+        <v>RI: L1=RVJ S-21</v>
       </c>
       <c r="Y23" t="str">
-        <v>Book shows one right arm on top of vertical stem</v>
+        <v>Book shows one left arm on top of vertical stem</v>
       </c>
       <c r="Z23">
         <v>250</v>
@@ -2103,13 +2103,13 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>RVJ S-22</v>
+        <v>RVJ S-8</v>
       </c>
       <c r="B24" t="str">
         <v>VDLR</v>
       </c>
       <c r="C24" t="str">
-        <v>Wadala road</v>
+        <v>Wadala Road</v>
       </c>
       <c r="D24" t="str">
         <v>CSMT-PNVL</v>
@@ -2121,19 +2121,19 @@
         <v>DN</v>
       </c>
       <c r="G24" t="str">
-        <v>10/H108</v>
+        <v>VDLR PF-3</v>
       </c>
       <c r="H24" t="str">
-        <v>10/H108</v>
-      </c>
-      <c r="I24">
-        <v>10.191</v>
-      </c>
-      <c r="J24">
-        <v>19.02566</v>
-      </c>
-      <c r="K24">
-        <v>72.86075</v>
+        <v/>
+      </c>
+      <c r="I24" t="str">
+        <v/>
+      </c>
+      <c r="J24" t="str">
+        <v/>
+      </c>
+      <c r="K24" t="str">
+        <v/>
       </c>
       <c r="L24" t="str">
         <v>Semi-Automatic</v>
@@ -2166,13 +2166,19 @@
         <v>0</v>
       </c>
       <c r="V24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W24">
         <v>0</v>
       </c>
+      <c r="X24" t="str">
+        <v>RI: L1=RVJ S-21</v>
+      </c>
+      <c r="Y24" t="str">
+        <v>Book shows one left arm on top of vertical stem</v>
+      </c>
       <c r="Z24">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="AA24">
         <v>1</v>
@@ -2180,7 +2186,13 @@
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>H-41</v>
+        <v>RVJ S-9</v>
+      </c>
+      <c r="B25" t="str">
+        <v>VDLR</v>
+      </c>
+      <c r="C25" t="str">
+        <v>Wadala road</v>
       </c>
       <c r="D25" t="str">
         <v>CSMT-PNVL</v>
@@ -2192,28 +2204,28 @@
         <v>DN</v>
       </c>
       <c r="G25" t="str">
-        <v>10/H166</v>
+        <v>09/H142</v>
       </c>
       <c r="H25" t="str">
-        <v>10/H166</v>
+        <v>09/H142</v>
       </c>
       <c r="I25">
-        <v>11.1</v>
+        <v>9.636</v>
       </c>
       <c r="J25">
-        <v>19.03338</v>
+        <v>19.02037</v>
       </c>
       <c r="K25">
-        <v>72.86107</v>
+        <v>72.86103</v>
       </c>
       <c r="L25" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M25" t="str">
         <v>Left</v>
       </c>
       <c r="N25" t="str">
-        <v>Right</v>
+        <v>Left</v>
       </c>
       <c r="O25">
         <v>0</v>
@@ -2231,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="T25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25">
         <v>0</v>
@@ -2240,10 +2252,16 @@
         <v>0</v>
       </c>
       <c r="W25">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X25" t="str">
+        <v>RI: R1=PNVL</v>
+      </c>
+      <c r="Y25" t="str">
+        <v>Book shows one right arm on top of vertical stem</v>
       </c>
       <c r="Z25">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="AA25">
         <v>1</v>
@@ -2251,7 +2269,13 @@
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>H-43</v>
+        <v>RVJ S-22</v>
+      </c>
+      <c r="B26" t="str">
+        <v>VDLR</v>
+      </c>
+      <c r="C26" t="str">
+        <v>Wadala road</v>
       </c>
       <c r="D26" t="str">
         <v>CSMT-PNVL</v>
@@ -2263,22 +2287,22 @@
         <v>DN</v>
       </c>
       <c r="G26" t="str">
-        <v>GTBN PF-1</v>
+        <v>10/H108</v>
       </c>
       <c r="H26" t="str">
-        <v>11/H17</v>
+        <v>10/H108</v>
       </c>
       <c r="I26">
-        <v>11.855</v>
+        <v>10.191</v>
       </c>
       <c r="J26">
-        <v>19.0391</v>
+        <v>19.02566</v>
       </c>
       <c r="K26">
-        <v>72.86523</v>
+        <v>72.86075</v>
       </c>
       <c r="L26" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M26" t="str">
         <v>Left</v>
@@ -2322,7 +2346,7 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>H-45</v>
+        <v>H-41</v>
       </c>
       <c r="D27" t="str">
         <v>CSMT-PNVL</v>
@@ -2334,37 +2358,37 @@
         <v>DN</v>
       </c>
       <c r="G27" t="str">
-        <v>12/H120</v>
+        <v>10/H166</v>
       </c>
       <c r="H27" t="str">
-        <v>12/H120</v>
+        <v>10/H166</v>
       </c>
       <c r="I27">
-        <v>12.505</v>
+        <v>11.1</v>
       </c>
       <c r="J27">
-        <v>19.0437</v>
+        <v>19.03338</v>
       </c>
       <c r="K27">
-        <v>72.86874</v>
+        <v>72.86107</v>
       </c>
       <c r="L27" t="str">
         <v>Automatic</v>
       </c>
       <c r="M27" t="str">
-        <v>Extreme Right</v>
+        <v>Left</v>
       </c>
       <c r="N27" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="O27">
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -2393,7 +2417,7 @@
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>H-47</v>
+        <v>H-43</v>
       </c>
       <c r="D28" t="str">
         <v>CSMT-PNVL</v>
@@ -2405,37 +2429,37 @@
         <v>DN</v>
       </c>
       <c r="G28" t="str">
-        <v>12/H146</v>
+        <v>GTBN PF-1</v>
       </c>
       <c r="H28" t="str">
-        <v>12/H146</v>
+        <v>11/H17</v>
       </c>
       <c r="I28">
-        <v>13.003</v>
+        <v>11.855</v>
       </c>
       <c r="J28">
-        <v>19.0481</v>
+        <v>19.0391</v>
       </c>
       <c r="K28">
-        <v>72.86951</v>
+        <v>72.86523</v>
       </c>
       <c r="L28" t="str">
         <v>Automatic</v>
       </c>
       <c r="M28" t="str">
-        <v>Extreme Right</v>
+        <v>Left</v>
       </c>
       <c r="N28" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="O28">
         <v>0</v>
       </c>
       <c r="P28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R28">
         <v>0</v>
@@ -2456,7 +2480,7 @@
         <v>0</v>
       </c>
       <c r="Z28">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="AA28">
         <v>1</v>
@@ -2464,7 +2488,7 @@
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>H-49</v>
+        <v>H-45</v>
       </c>
       <c r="D29" t="str">
         <v>CSMT-PNVL</v>
@@ -2476,37 +2500,37 @@
         <v>DN</v>
       </c>
       <c r="G29" t="str">
-        <v>CHF PF-1</v>
+        <v>12/H120</v>
       </c>
       <c r="H29" t="str">
-        <v>13/H05</v>
+        <v>12/H120</v>
       </c>
       <c r="I29">
-        <v>13.436</v>
+        <v>12.505</v>
       </c>
       <c r="J29">
-        <v>19.05197</v>
+        <v>19.0437</v>
       </c>
       <c r="K29">
-        <v>72.869</v>
+        <v>72.86874</v>
       </c>
       <c r="L29" t="str">
         <v>Automatic</v>
       </c>
       <c r="M29" t="str">
-        <v>Left</v>
+        <v>Extreme Right</v>
       </c>
       <c r="N29" t="str">
-        <v>Right</v>
+        <v>Left</v>
       </c>
       <c r="O29">
         <v>0</v>
       </c>
       <c r="P29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q29">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -2527,7 +2551,7 @@
         <v>0</v>
       </c>
       <c r="Z29">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="AA29">
         <v>1</v>
@@ -2535,13 +2559,7 @@
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>CLA S-5</v>
-      </c>
-      <c r="B30" t="str">
-        <v>CLA</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Kurla</v>
+        <v>H-47</v>
       </c>
       <c r="D30" t="str">
         <v>CSMT-PNVL</v>
@@ -2553,37 +2571,37 @@
         <v>DN</v>
       </c>
       <c r="G30" t="str">
-        <v>13/H140</v>
+        <v>12/H146</v>
       </c>
       <c r="H30" t="str">
-        <v>13/H140</v>
+        <v>12/H146</v>
       </c>
       <c r="I30">
-        <v>13.722</v>
+        <v>13.003</v>
       </c>
       <c r="J30">
-        <v>19.05528</v>
+        <v>19.0481</v>
       </c>
       <c r="K30">
-        <v>72.86973</v>
+        <v>72.86951</v>
       </c>
       <c r="L30" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M30" t="str">
-        <v>Left</v>
+        <v>Extreme Right</v>
       </c>
       <c r="N30" t="str">
-        <v>Right</v>
+        <v>Left</v>
       </c>
       <c r="O30">
         <v>0</v>
       </c>
       <c r="P30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -2592,7 +2610,7 @@
         <v>0</v>
       </c>
       <c r="T30">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30">
         <v>0</v>
@@ -2601,16 +2619,10 @@
         <v>0</v>
       </c>
       <c r="W30">
-        <v>1</v>
-      </c>
-      <c r="X30" t="str">
-        <v>RI: R1=CLA GOODS</v>
-      </c>
-      <c r="Y30" t="str">
-        <v>Book shows one right arm on top of vertical stem</v>
+        <v>0</v>
       </c>
       <c r="Z30">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="AA30">
         <v>1</v>
@@ -2618,13 +2630,7 @@
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>CLA S-2</v>
-      </c>
-      <c r="B31" t="str">
-        <v>CLA</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Kurla</v>
+        <v>H-49</v>
       </c>
       <c r="D31" t="str">
         <v>CSMT-PNVL</v>
@@ -2636,25 +2642,25 @@
         <v>DN</v>
       </c>
       <c r="G31" t="str">
-        <v>14/H138</v>
+        <v>CHF PF-1</v>
       </c>
       <c r="H31" t="str">
-        <v>14/H138</v>
+        <v>13/H05</v>
       </c>
       <c r="I31">
-        <v>14.784</v>
+        <v>13.436</v>
       </c>
       <c r="J31">
-        <v>19.06214</v>
+        <v>19.05197</v>
       </c>
       <c r="K31">
-        <v>72.87536</v>
+        <v>72.869</v>
       </c>
       <c r="L31" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M31" t="str">
-        <v>Extreme Right</v>
+        <v>Left</v>
       </c>
       <c r="N31" t="str">
         <v>Right</v>
@@ -2663,10 +2669,10 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -2675,7 +2681,7 @@
         <v>0</v>
       </c>
       <c r="T31">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U31">
         <v>0</v>
@@ -2684,16 +2690,10 @@
         <v>0</v>
       </c>
       <c r="W31">
-        <v>1</v>
-      </c>
-      <c r="X31" t="str">
-        <v>RI: R1=PF-8</v>
-      </c>
-      <c r="Y31" t="str">
-        <v>Book shows one right arm on top of vertical stem</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AA31">
         <v>1</v>
@@ -2701,7 +2701,7 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>CLA S-12</v>
+        <v>CLA S-5</v>
       </c>
       <c r="B32" t="str">
         <v>CLA</v>
@@ -2719,37 +2719,37 @@
         <v>DN</v>
       </c>
       <c r="G32" t="str">
-        <v>PF-7 STR</v>
+        <v>13/H140</v>
       </c>
       <c r="H32" t="str">
-        <v>15/H15</v>
+        <v>13/H140</v>
       </c>
       <c r="I32">
-        <v>15.481</v>
+        <v>13.722</v>
       </c>
       <c r="J32">
-        <v>19.06589</v>
+        <v>19.05528</v>
       </c>
       <c r="K32">
-        <v>72.88057</v>
+        <v>72.86973</v>
       </c>
       <c r="L32" t="str">
         <v>Semi-Automatic</v>
       </c>
       <c r="M32" t="str">
+        <v>Left</v>
+      </c>
+      <c r="N32" t="str">
         <v>Right</v>
       </c>
-      <c r="N32" t="str">
-        <v>Unknown</v>
-      </c>
       <c r="O32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32">
         <v>0</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R32">
         <v>0</v>
@@ -2761,19 +2761,19 @@
         <v>1</v>
       </c>
       <c r="U32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V32">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X32" t="str">
-        <v>RI: L1=CLA YD</v>
+        <v>RI: R1=CLA GOODS</v>
       </c>
       <c r="Y32" t="str">
-        <v>Book shows one left arm on top of vertical stem</v>
+        <v>Book shows one right arm on top of vertical stem</v>
       </c>
       <c r="Z32">
         <v>300</v>
@@ -2784,7 +2784,13 @@
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>H-51</v>
+        <v>CLA S-2</v>
+      </c>
+      <c r="B33" t="str">
+        <v>CLA</v>
+      </c>
+      <c r="C33" t="str">
+        <v>Kurla</v>
       </c>
       <c r="D33" t="str">
         <v>CSMT-PNVL</v>
@@ -2796,37 +2802,37 @@
         <v>DN</v>
       </c>
       <c r="G33" t="str">
-        <v>16/H116</v>
+        <v>14/H138</v>
       </c>
       <c r="H33" t="str">
-        <v>16/H116</v>
+        <v>14/H138</v>
       </c>
       <c r="I33">
-        <v>16.225</v>
+        <v>14.784</v>
       </c>
       <c r="J33">
-        <v>19.06665</v>
+        <v>19.06214</v>
       </c>
       <c r="K33">
-        <v>72.88725</v>
+        <v>72.87536</v>
       </c>
       <c r="L33" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M33" t="str">
-        <v>Left</v>
+        <v>Extreme Right</v>
       </c>
       <c r="N33" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="O33">
         <v>0</v>
       </c>
       <c r="P33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q33">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -2835,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="T33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33">
         <v>0</v>
@@ -2844,10 +2850,16 @@
         <v>0</v>
       </c>
       <c r="W33">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X33" t="str">
+        <v>RI: R1=PF-8</v>
+      </c>
+      <c r="Y33" t="str">
+        <v>Book shows one right arm on top of vertical stem</v>
       </c>
       <c r="Z33">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AA33">
         <v>1</v>
@@ -2855,7 +2867,13 @@
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>H-53</v>
+        <v>CLA S-12</v>
+      </c>
+      <c r="B34" t="str">
+        <v>CLA</v>
+      </c>
+      <c r="C34" t="str">
+        <v>Kurla</v>
       </c>
       <c r="D34" t="str">
         <v>CSMT-PNVL</v>
@@ -2867,37 +2885,37 @@
         <v>DN</v>
       </c>
       <c r="G34" t="str">
-        <v>TKNG PF-1 STR</v>
+        <v>PF-7 STR</v>
       </c>
       <c r="H34" t="str">
-        <v>16/H11</v>
+        <v>15/H15</v>
       </c>
       <c r="I34">
-        <v>16.722</v>
+        <v>15.481</v>
       </c>
       <c r="J34">
-        <v>19.06547</v>
+        <v>19.06589</v>
       </c>
       <c r="K34">
-        <v>72.89166</v>
+        <v>72.88057</v>
       </c>
       <c r="L34" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M34" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="N34" t="str">
         <v>Unknown</v>
       </c>
       <c r="O34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P34">
         <v>0</v>
       </c>
       <c r="Q34">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -2906,19 +2924,25 @@
         <v>0</v>
       </c>
       <c r="T34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W34">
         <v>0</v>
       </c>
+      <c r="X34" t="str">
+        <v>RI: L1=CLA YD</v>
+      </c>
+      <c r="Y34" t="str">
+        <v>Book shows one left arm on top of vertical stem</v>
+      </c>
       <c r="Z34">
-        <v>700</v>
+        <v>300</v>
       </c>
       <c r="AA34">
         <v>1</v>
@@ -2926,13 +2950,7 @@
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>CMBR S-10</v>
-      </c>
-      <c r="B35" t="str">
-        <v>CMBR</v>
-      </c>
-      <c r="C35" t="str">
-        <v>Chembur</v>
+        <v>H-51</v>
       </c>
       <c r="D35" t="str">
         <v>CSMT-PNVL</v>
@@ -2944,22 +2962,22 @@
         <v>DN</v>
       </c>
       <c r="G35" t="str">
-        <v>17/H118</v>
+        <v>16/H116</v>
       </c>
       <c r="H35" t="str">
-        <v>17/H118</v>
+        <v>16/H116</v>
       </c>
       <c r="I35">
-        <v>17.414</v>
+        <v>16.225</v>
       </c>
       <c r="J35">
-        <v>19.06392</v>
+        <v>19.06665</v>
       </c>
       <c r="K35">
-        <v>72.89799</v>
+        <v>72.88725</v>
       </c>
       <c r="L35" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M35" t="str">
         <v>Left</v>
@@ -2995,7 +3013,7 @@
         <v>0</v>
       </c>
       <c r="Z35">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AA35">
         <v>1</v>
@@ -3003,13 +3021,7 @@
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>CMBR S-9</v>
-      </c>
-      <c r="B36" t="str">
-        <v>CMBR</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Chembur</v>
+        <v>H-53</v>
       </c>
       <c r="D36" t="str">
         <v>CSMT-PNVL</v>
@@ -3021,22 +3033,22 @@
         <v>DN</v>
       </c>
       <c r="G36" t="str">
-        <v>CMBR PF-1</v>
+        <v>TKNG PF-1 STR</v>
       </c>
       <c r="H36" t="str">
-        <v>18/H01</v>
+        <v>16/H11</v>
       </c>
       <c r="I36">
-        <v>17.97</v>
+        <v>16.722</v>
       </c>
       <c r="J36">
-        <v>19.06197</v>
+        <v>19.06547</v>
       </c>
       <c r="K36">
-        <v>72.90284</v>
+        <v>72.89166</v>
       </c>
       <c r="L36" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M36" t="str">
         <v>Left</v>
@@ -3072,7 +3084,7 @@
         <v>0</v>
       </c>
       <c r="Z36">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AA36">
         <v>1</v>
@@ -3080,7 +3092,13 @@
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>H-55</v>
+        <v>CMBR S-10</v>
+      </c>
+      <c r="B37" t="str">
+        <v>CMBR</v>
+      </c>
+      <c r="C37" t="str">
+        <v>Chembur</v>
       </c>
       <c r="D37" t="str">
         <v>CSMT-PNVL</v>
@@ -3092,22 +3110,22 @@
         <v>DN</v>
       </c>
       <c r="G37" t="str">
-        <v>18/H124</v>
+        <v>17/H118</v>
       </c>
       <c r="H37" t="str">
-        <v>18/H124</v>
+        <v>17/H118</v>
       </c>
       <c r="I37">
-        <v>18.483</v>
+        <v>17.414</v>
       </c>
       <c r="J37">
-        <v>19.05993</v>
+        <v>19.06392</v>
       </c>
       <c r="K37">
-        <v>72.90717</v>
+        <v>72.89799</v>
       </c>
       <c r="L37" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M37" t="str">
         <v>Left</v>
@@ -3143,7 +3161,7 @@
         <v>0</v>
       </c>
       <c r="Z37">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AA37">
         <v>1</v>
@@ -3151,7 +3169,13 @@
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>H-57</v>
+        <v>CMBR S-9</v>
+      </c>
+      <c r="B38" t="str">
+        <v>CMBR</v>
+      </c>
+      <c r="C38" t="str">
+        <v>Chembur</v>
       </c>
       <c r="D38" t="str">
         <v>CSMT-PNVL</v>
@@ -3163,28 +3187,28 @@
         <v>DN</v>
       </c>
       <c r="G38" t="str">
-        <v>19/H102</v>
+        <v>CMBR PF-1</v>
       </c>
       <c r="H38" t="str">
-        <v>19/H102</v>
+        <v>18/H01</v>
       </c>
       <c r="I38">
-        <v>19.003</v>
+        <v>17.97</v>
       </c>
       <c r="J38">
-        <v>19.05767</v>
+        <v>19.06197</v>
       </c>
       <c r="K38">
-        <v>72.91166</v>
+        <v>72.90284</v>
       </c>
       <c r="L38" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M38" t="str">
         <v>Left</v>
       </c>
       <c r="N38" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="O38">
         <v>0</v>
@@ -3214,7 +3238,7 @@
         <v>0</v>
       </c>
       <c r="Z38">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="AA38">
         <v>1</v>
@@ -3222,7 +3246,7 @@
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>H-59</v>
+        <v>H-55</v>
       </c>
       <c r="D39" t="str">
         <v>CSMT-PNVL</v>
@@ -3234,19 +3258,19 @@
         <v>DN</v>
       </c>
       <c r="G39" t="str">
-        <v>GV PF-1</v>
+        <v>18/H124</v>
       </c>
       <c r="H39" t="str">
-        <v>19/H10</v>
+        <v>18/H124</v>
       </c>
       <c r="I39">
-        <v>19.615</v>
+        <v>18.483</v>
       </c>
       <c r="J39">
-        <v>19.05462</v>
+        <v>19.05993</v>
       </c>
       <c r="K39">
-        <v>72.91642</v>
+        <v>72.90717</v>
       </c>
       <c r="L39" t="str">
         <v>Automatic</v>
@@ -3285,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="Z39">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AA39">
         <v>1</v>
@@ -3293,7 +3317,7 @@
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>H-61</v>
+        <v>H-57</v>
       </c>
       <c r="D40" t="str">
         <v>CSMT-PNVL</v>
@@ -3305,19 +3329,19 @@
         <v>DN</v>
       </c>
       <c r="G40" t="str">
-        <v>20/H108</v>
+        <v>19/H102</v>
       </c>
       <c r="H40" t="str">
-        <v>20/H108</v>
+        <v>19/H102</v>
       </c>
       <c r="I40">
-        <v>20.19</v>
+        <v>19.003</v>
       </c>
       <c r="J40">
-        <v>19.05175</v>
+        <v>19.05767</v>
       </c>
       <c r="K40">
-        <v>72.92094</v>
+        <v>72.91166</v>
       </c>
       <c r="L40" t="str">
         <v>Automatic</v>
@@ -3326,7 +3350,7 @@
         <v>Left</v>
       </c>
       <c r="N40" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="O40">
         <v>0</v>
@@ -3356,7 +3380,7 @@
         <v>0</v>
       </c>
       <c r="Z40">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AA40">
         <v>1</v>
@@ -3364,13 +3388,7 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>MNKD S-1</v>
-      </c>
-      <c r="B41" t="str">
-        <v>MNKD</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Mankhurd</v>
+        <v>H-59</v>
       </c>
       <c r="D41" t="str">
         <v>CSMT-PNVL</v>
@@ -3382,28 +3400,28 @@
         <v>DN</v>
       </c>
       <c r="G41" t="str">
-        <v>20/H130</v>
+        <v>GV PF-1</v>
       </c>
       <c r="H41" t="str">
-        <v>20/H130</v>
+        <v>19/H10</v>
       </c>
       <c r="I41">
-        <v>20.694</v>
+        <v>19.615</v>
       </c>
       <c r="J41">
-        <v>19.04941</v>
+        <v>19.05462</v>
       </c>
       <c r="K41">
-        <v>72.92508</v>
+        <v>72.91642</v>
       </c>
       <c r="L41" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M41" t="str">
         <v>Left</v>
       </c>
       <c r="N41" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="O41">
         <v>0</v>
@@ -3421,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="T41">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U41">
         <v>0</v>
@@ -3430,16 +3448,10 @@
         <v>0</v>
       </c>
       <c r="W41">
-        <v>2</v>
-      </c>
-      <c r="X41" t="str">
-        <v>RI: R1=PF-2; R2=PF-3</v>
-      </c>
-      <c r="Y41" t="str">
-        <v>Book shows two right arms on top of vertical stem</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AA41">
         <v>1</v>
@@ -3447,13 +3459,7 @@
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>MNKD S-2</v>
-      </c>
-      <c r="B42" t="str">
-        <v>MNKD</v>
-      </c>
-      <c r="C42" t="str">
-        <v>Mankhurd</v>
+        <v>H-61</v>
       </c>
       <c r="D42" t="str">
         <v>CSMT-PNVL</v>
@@ -3465,22 +3471,22 @@
         <v>DN</v>
       </c>
       <c r="G42" t="str">
-        <v>21/H104</v>
+        <v>20/H108</v>
       </c>
       <c r="H42" t="str">
-        <v>21/H104</v>
+        <v>20/H108</v>
       </c>
       <c r="I42">
-        <v>21.084</v>
+        <v>20.19</v>
       </c>
       <c r="J42">
-        <v>19.04821</v>
+        <v>19.05175</v>
       </c>
       <c r="K42">
-        <v>72.92847</v>
+        <v>72.92094</v>
       </c>
       <c r="L42" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M42" t="str">
         <v>Left</v>
@@ -3516,7 +3522,7 @@
         <v>0</v>
       </c>
       <c r="Z42">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AA42">
         <v>1</v>
@@ -3524,7 +3530,7 @@
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>MNKD S-4</v>
+        <v>MNKD S-1</v>
       </c>
       <c r="B43" t="str">
         <v>MNKD</v>
@@ -3542,19 +3548,19 @@
         <v>DN</v>
       </c>
       <c r="G43" t="str">
-        <v>MNKD PF-1 STR</v>
+        <v>20/H130</v>
       </c>
       <c r="H43" t="str">
-        <v>21/H13</v>
+        <v>20/H130</v>
       </c>
       <c r="I43">
-        <v>21.607</v>
+        <v>20.694</v>
       </c>
       <c r="J43">
-        <v>19.04896</v>
+        <v>19.04941</v>
       </c>
       <c r="K43">
-        <v>72.93308</v>
+        <v>72.92508</v>
       </c>
       <c r="L43" t="str">
         <v>Semi-Automatic</v>
@@ -3581,7 +3587,7 @@
         <v>0</v>
       </c>
       <c r="T43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U43">
         <v>0</v>
@@ -3590,10 +3596,16 @@
         <v>0</v>
       </c>
       <c r="W43">
-        <v>0</v>
+        <v>2</v>
+      </c>
+      <c r="X43" t="str">
+        <v>RI: R1=PF-2; R2=PF-3</v>
+      </c>
+      <c r="Y43" t="str">
+        <v>Book shows two right arms on top of vertical stem</v>
       </c>
       <c r="Z43">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="AA43">
         <v>1</v>
@@ -3601,7 +3613,13 @@
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>H-2201</v>
+        <v>MNKD S-2</v>
+      </c>
+      <c r="B44" t="str">
+        <v>MNKD</v>
+      </c>
+      <c r="C44" t="str">
+        <v>Mankhurd</v>
       </c>
       <c r="D44" t="str">
         <v>CSMT-PNVL</v>
@@ -3613,22 +3631,22 @@
         <v>DN</v>
       </c>
       <c r="G44" t="str">
-        <v>21/H180</v>
+        <v>21/H104</v>
       </c>
       <c r="H44" t="str">
-        <v>21/H180</v>
+        <v>21/H104</v>
       </c>
       <c r="I44">
-        <v>21.985</v>
+        <v>21.084</v>
       </c>
       <c r="J44">
-        <v>19.05039</v>
+        <v>19.04821</v>
       </c>
       <c r="K44">
-        <v>72.9363</v>
+        <v>72.92847</v>
       </c>
       <c r="L44" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M44" t="str">
         <v>Left</v>
@@ -3664,7 +3682,7 @@
         <v>0</v>
       </c>
       <c r="Z44">
-        <v>300</v>
+        <v>350</v>
       </c>
       <c r="AA44">
         <v>1</v>
@@ -3672,7 +3690,13 @@
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>H-2209</v>
+        <v>MNKD S-4</v>
+      </c>
+      <c r="B45" t="str">
+        <v>MNKD</v>
+      </c>
+      <c r="C45" t="str">
+        <v>Mankhurd</v>
       </c>
       <c r="D45" t="str">
         <v>CSMT-PNVL</v>
@@ -3684,28 +3708,28 @@
         <v>DN</v>
       </c>
       <c r="G45" t="str">
-        <v>22/H116</v>
+        <v>MNKD PF-1 STR</v>
       </c>
       <c r="H45" t="str">
-        <v>22/H116</v>
+        <v>21/H13</v>
       </c>
       <c r="I45">
-        <v>22.385</v>
+        <v>21.607</v>
       </c>
       <c r="J45">
-        <v>19.05154</v>
+        <v>19.04896</v>
       </c>
       <c r="K45">
-        <v>72.9398</v>
+        <v>72.93308</v>
       </c>
       <c r="L45" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M45" t="str">
         <v>Left</v>
       </c>
       <c r="N45" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="O45">
         <v>0</v>
@@ -3735,7 +3759,7 @@
         <v>0</v>
       </c>
       <c r="Z45">
-        <v>400</v>
+        <v>180</v>
       </c>
       <c r="AA45">
         <v>1</v>
@@ -3743,7 +3767,7 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>H-2215</v>
+        <v>H-2201</v>
       </c>
       <c r="D46" t="str">
         <v>CSMT-PNVL</v>
@@ -3755,19 +3779,19 @@
         <v>DN</v>
       </c>
       <c r="G46" t="str">
-        <v>22/H136</v>
+        <v>21/H180</v>
       </c>
       <c r="H46" t="str">
-        <v>22/H136</v>
+        <v>21/H180</v>
       </c>
       <c r="I46">
-        <v>22.78</v>
+        <v>21.985</v>
       </c>
       <c r="J46">
-        <v>19.05282</v>
+        <v>19.05039</v>
       </c>
       <c r="K46">
-        <v>72.94338</v>
+        <v>72.9363</v>
       </c>
       <c r="L46" t="str">
         <v>Automatic</v>
@@ -3806,7 +3830,7 @@
         <v>0</v>
       </c>
       <c r="Z46">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="AA46">
         <v>1</v>
@@ -3814,7 +3838,7 @@
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>H-2305</v>
+        <v>H-2209</v>
       </c>
       <c r="D47" t="str">
         <v>CSMT-PNVL</v>
@@ -3826,19 +3850,19 @@
         <v>DN</v>
       </c>
       <c r="G47" t="str">
-        <v>23/H108</v>
+        <v>22/H116</v>
       </c>
       <c r="H47" t="str">
-        <v>23/H108</v>
+        <v>22/H116</v>
       </c>
       <c r="I47">
-        <v>23.2</v>
+        <v>22.385</v>
       </c>
       <c r="J47">
-        <v>19.05416</v>
+        <v>19.05154</v>
       </c>
       <c r="K47">
-        <v>72.94716</v>
+        <v>72.9398</v>
       </c>
       <c r="L47" t="str">
         <v>Automatic</v>
@@ -3877,7 +3901,7 @@
         <v>0</v>
       </c>
       <c r="Z47">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="AA47">
         <v>1</v>
@@ -3885,7 +3909,7 @@
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>H-2311</v>
+        <v>H-2215</v>
       </c>
       <c r="D48" t="str">
         <v>CSMT-PNVL</v>
@@ -3897,19 +3921,19 @@
         <v>DN</v>
       </c>
       <c r="G48" t="str">
-        <v>23/H128</v>
+        <v>22/H136</v>
       </c>
       <c r="H48" t="str">
-        <v>23/H128</v>
+        <v>22/H136</v>
       </c>
       <c r="I48">
-        <v>23.646</v>
+        <v>22.78</v>
       </c>
       <c r="J48">
-        <v>19.05558</v>
+        <v>19.05282</v>
       </c>
       <c r="K48">
-        <v>72.95143</v>
+        <v>72.94338</v>
       </c>
       <c r="L48" t="str">
         <v>Automatic</v>
@@ -3918,7 +3942,7 @@
         <v>Left</v>
       </c>
       <c r="N48" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="O48">
         <v>0</v>
@@ -3948,7 +3972,7 @@
         <v>0</v>
       </c>
       <c r="Z48">
-        <v>1200</v>
+        <v>800</v>
       </c>
       <c r="AA48">
         <v>1</v>
@@ -3956,7 +3980,7 @@
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>H-2401</v>
+        <v>H-2305</v>
       </c>
       <c r="D49" t="str">
         <v>CSMT-PNVL</v>
@@ -3968,19 +3992,19 @@
         <v>DN</v>
       </c>
       <c r="G49" t="str">
-        <v>24/H102</v>
+        <v>23/H108</v>
       </c>
       <c r="H49" t="str">
-        <v>24/H102</v>
+        <v>23/H108</v>
       </c>
       <c r="I49">
-        <v>24.028</v>
+        <v>23.2</v>
       </c>
       <c r="J49">
-        <v>19.05651</v>
+        <v>19.05416</v>
       </c>
       <c r="K49">
-        <v>72.95458</v>
+        <v>72.94716</v>
       </c>
       <c r="L49" t="str">
         <v>Automatic</v>
@@ -4019,7 +4043,7 @@
         <v>0</v>
       </c>
       <c r="Z49">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="AA49">
         <v>1</v>
@@ -4027,7 +4051,7 @@
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>H-2411</v>
+        <v>H-2311</v>
       </c>
       <c r="D50" t="str">
         <v>CSMT-PNVL</v>
@@ -4039,19 +4063,19 @@
         <v>DN</v>
       </c>
       <c r="G50" t="str">
-        <v>24/H130</v>
+        <v>23/H128</v>
       </c>
       <c r="H50" t="str">
-        <v>24/H130</v>
+        <v>23/H128</v>
       </c>
       <c r="I50">
-        <v>24.637</v>
+        <v>23.646</v>
       </c>
       <c r="J50">
-        <v>19.05806</v>
+        <v>19.05558</v>
       </c>
       <c r="K50">
-        <v>72.96032</v>
+        <v>72.95143</v>
       </c>
       <c r="L50" t="str">
         <v>Automatic</v>
@@ -4060,7 +4084,7 @@
         <v>Left</v>
       </c>
       <c r="N50" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="O50">
         <v>0</v>
@@ -4090,7 +4114,7 @@
         <v>0</v>
       </c>
       <c r="Z50">
-        <v>800</v>
+        <v>1200</v>
       </c>
       <c r="AA50">
         <v>1</v>
@@ -4098,7 +4122,7 @@
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>H-2503</v>
+        <v>H-2401</v>
       </c>
       <c r="D51" t="str">
         <v>CSMT-PNVL</v>
@@ -4110,19 +4134,19 @@
         <v>DN</v>
       </c>
       <c r="G51" t="str">
-        <v>25/H106</v>
+        <v>24/H102</v>
       </c>
       <c r="H51" t="str">
-        <v>25/H106</v>
+        <v>24/H102</v>
       </c>
       <c r="I51">
-        <v>25.164</v>
+        <v>24.028</v>
       </c>
       <c r="J51">
-        <v>19.0592</v>
+        <v>19.05651</v>
       </c>
       <c r="K51">
-        <v>72.96515</v>
+        <v>72.95458</v>
       </c>
       <c r="L51" t="str">
         <v>Automatic</v>
@@ -4169,7 +4193,7 @@
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>H-2513</v>
+        <v>H-2411</v>
       </c>
       <c r="D52" t="str">
         <v>CSMT-PNVL</v>
@@ -4181,19 +4205,19 @@
         <v>DN</v>
       </c>
       <c r="G52" t="str">
-        <v>25/H124</v>
+        <v>24/H130</v>
       </c>
       <c r="H52" t="str">
-        <v>25/H124</v>
+        <v>24/H130</v>
       </c>
       <c r="I52">
-        <v>25.66</v>
+        <v>24.637</v>
       </c>
       <c r="J52">
-        <v>19.06025</v>
+        <v>19.05806</v>
       </c>
       <c r="K52">
-        <v>72.9696</v>
+        <v>72.96032</v>
       </c>
       <c r="L52" t="str">
         <v>Automatic</v>
@@ -4232,7 +4256,7 @@
         <v>0</v>
       </c>
       <c r="Z52">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AA52">
         <v>1</v>
@@ -4240,7 +4264,7 @@
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>H-2603</v>
+        <v>H-2503</v>
       </c>
       <c r="D53" t="str">
         <v>CSMT-PNVL</v>
@@ -4252,19 +4276,19 @@
         <v>DN</v>
       </c>
       <c r="G53" t="str">
-        <v>26/H104</v>
+        <v>25/H106</v>
       </c>
       <c r="H53" t="str">
-        <v>26/H104</v>
+        <v>25/H106</v>
       </c>
       <c r="I53">
-        <v>26.142</v>
+        <v>25.164</v>
       </c>
       <c r="J53">
-        <v>19.06129</v>
+        <v>19.0592</v>
       </c>
       <c r="K53">
-        <v>72.97403</v>
+        <v>72.96515</v>
       </c>
       <c r="L53" t="str">
         <v>Automatic</v>
@@ -4303,7 +4327,7 @@
         <v>0</v>
       </c>
       <c r="Z53">
-        <v>600</v>
+        <v>800</v>
       </c>
       <c r="AA53">
         <v>1</v>
@@ -4311,7 +4335,7 @@
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>H-2613</v>
+        <v>H-2513</v>
       </c>
       <c r="D54" t="str">
         <v>CSMT-PNVL</v>
@@ -4323,19 +4347,19 @@
         <v>DN</v>
       </c>
       <c r="G54" t="str">
-        <v>26/H124</v>
+        <v>25/H124</v>
       </c>
       <c r="H54" t="str">
-        <v>26/H124</v>
+        <v>25/H124</v>
       </c>
       <c r="I54">
-        <v>26.666</v>
+        <v>25.66</v>
       </c>
       <c r="J54">
-        <v>19.06242</v>
+        <v>19.06025</v>
       </c>
       <c r="K54">
-        <v>72.97891</v>
+        <v>72.9696</v>
       </c>
       <c r="L54" t="str">
         <v>Automatic</v>
@@ -4374,7 +4398,7 @@
         <v>0</v>
       </c>
       <c r="Z54">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="AA54">
         <v>1</v>
@@ -4382,7 +4406,7 @@
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>H-2703</v>
+        <v>H-2603</v>
       </c>
       <c r="D55" t="str">
         <v>CSMT-PNVL</v>
@@ -4394,19 +4418,19 @@
         <v>DN</v>
       </c>
       <c r="G55" t="str">
-        <v>27/H104</v>
+        <v>26/H104</v>
       </c>
       <c r="H55" t="str">
-        <v>27/H104</v>
+        <v>26/H104</v>
       </c>
       <c r="I55">
-        <v>27.089</v>
+        <v>26.142</v>
       </c>
       <c r="J55">
-        <v>19.06313</v>
+        <v>19.06129</v>
       </c>
       <c r="K55">
-        <v>72.98287</v>
+        <v>72.97403</v>
       </c>
       <c r="L55" t="str">
         <v>Automatic</v>
@@ -4415,7 +4439,7 @@
         <v>Left</v>
       </c>
       <c r="N55" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="O55">
         <v>0</v>
@@ -4445,7 +4469,7 @@
         <v>0</v>
       </c>
       <c r="Z55">
-        <v>350</v>
+        <v>600</v>
       </c>
       <c r="AA55">
         <v>1</v>
@@ -4453,7 +4477,7 @@
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>H-2707</v>
+        <v>H-2613</v>
       </c>
       <c r="D56" t="str">
         <v>CSMT-PNVL</v>
@@ -4465,19 +4489,19 @@
         <v>DN</v>
       </c>
       <c r="G56" t="str">
-        <v>27/H122</v>
+        <v>26/H124</v>
       </c>
       <c r="H56" t="str">
-        <v>27/H122</v>
+        <v>26/H124</v>
       </c>
       <c r="I56">
-        <v>27.483</v>
+        <v>26.666</v>
       </c>
       <c r="J56">
-        <v>19.06232</v>
+        <v>19.06242</v>
       </c>
       <c r="K56">
-        <v>72.98663</v>
+        <v>72.97891</v>
       </c>
       <c r="L56" t="str">
         <v>Automatic</v>
@@ -4486,7 +4510,7 @@
         <v>Left</v>
       </c>
       <c r="N56" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="O56">
         <v>0</v>
@@ -4516,7 +4540,7 @@
         <v>0</v>
       </c>
       <c r="Z56">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AA56">
         <v>1</v>
@@ -4524,7 +4548,7 @@
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>H-2715</v>
+        <v>H-2703</v>
       </c>
       <c r="D57" t="str">
         <v>CSMT-PNVL</v>
@@ -4536,19 +4560,19 @@
         <v>DN</v>
       </c>
       <c r="G57" t="str">
-        <v>27/H138</v>
+        <v>27/H104</v>
       </c>
       <c r="H57" t="str">
-        <v>27/H138</v>
+        <v>27/H104</v>
       </c>
       <c r="I57">
-        <v>27.889</v>
+        <v>27.089</v>
       </c>
       <c r="J57">
-        <v>19.06065</v>
+        <v>19.06313</v>
       </c>
       <c r="K57">
-        <v>72.99046</v>
+        <v>72.98287</v>
       </c>
       <c r="L57" t="str">
         <v>Automatic</v>
@@ -4557,7 +4581,7 @@
         <v>Left</v>
       </c>
       <c r="N57" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="O57">
         <v>0</v>
@@ -4587,7 +4611,7 @@
         <v>0</v>
       </c>
       <c r="Z57">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="AA57">
         <v>1</v>
@@ -4595,13 +4619,7 @@
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>VSH S-2</v>
-      </c>
-      <c r="B58" t="str">
-        <v>VSH</v>
-      </c>
-      <c r="C58" t="str">
-        <v>Vashi</v>
+        <v>H-2707</v>
       </c>
       <c r="D58" t="str">
         <v>CSMT-PNVL</v>
@@ -4613,28 +4631,28 @@
         <v>DN</v>
       </c>
       <c r="G58" t="str">
-        <v>28/H118</v>
+        <v>27/H122</v>
       </c>
       <c r="H58" t="str">
-        <v>28/H118</v>
+        <v>27/H122</v>
       </c>
       <c r="I58">
-        <v>28.326</v>
+        <v>27.483</v>
       </c>
       <c r="J58">
-        <v>19.06064</v>
+        <v>19.06232</v>
       </c>
       <c r="K58">
-        <v>72.99382</v>
+        <v>72.98663</v>
       </c>
       <c r="L58" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M58" t="str">
         <v>Left</v>
       </c>
       <c r="N58" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="O58">
         <v>0</v>
@@ -4652,7 +4670,7 @@
         <v>0</v>
       </c>
       <c r="T58">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U58">
         <v>0</v>
@@ -4664,7 +4682,7 @@
         <v>0</v>
       </c>
       <c r="Z58">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="AA58">
         <v>1</v>
@@ -4672,13 +4690,7 @@
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>VSH S-5</v>
-      </c>
-      <c r="B59" t="str">
-        <v>VSH</v>
-      </c>
-      <c r="C59" t="str">
-        <v>Vashi</v>
+        <v>H-2715</v>
       </c>
       <c r="D59" t="str">
         <v>CSMT-PNVL</v>
@@ -4690,28 +4702,28 @@
         <v>DN</v>
       </c>
       <c r="G59" t="str">
-        <v>29/H102</v>
+        <v>27/H138</v>
       </c>
       <c r="H59" t="str">
-        <v>29/H102</v>
+        <v>27/H138</v>
       </c>
       <c r="I59">
-        <v>29.044</v>
+        <v>27.889</v>
       </c>
       <c r="J59">
-        <v>19.06359</v>
+        <v>19.06065</v>
       </c>
       <c r="K59">
-        <v>73.0002</v>
+        <v>72.99046</v>
       </c>
       <c r="L59" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M59" t="str">
         <v>Left</v>
       </c>
       <c r="N59" t="str">
-        <v>Right</v>
+        <v>Left</v>
       </c>
       <c r="O59">
         <v>0</v>
@@ -4732,7 +4744,7 @@
         <v>0</v>
       </c>
       <c r="U59">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V59">
         <v>0</v>
@@ -4741,7 +4753,7 @@
         <v>0</v>
       </c>
       <c r="Z59">
-        <v>200</v>
+        <v>600</v>
       </c>
       <c r="AA59">
         <v>1</v>
@@ -4749,7 +4761,13 @@
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>H-2921</v>
+        <v>VSH S-2</v>
+      </c>
+      <c r="B60" t="str">
+        <v>VSH</v>
+      </c>
+      <c r="C60" t="str">
+        <v>Vashi</v>
       </c>
       <c r="D60" t="str">
         <v>CSMT-PNVL</v>
@@ -4761,28 +4779,28 @@
         <v>DN</v>
       </c>
       <c r="G60" t="str">
-        <v>29/H120</v>
+        <v>28/H118</v>
       </c>
       <c r="H60" t="str">
-        <v>29/H120</v>
+        <v>28/H118</v>
       </c>
       <c r="I60">
-        <v>29.402</v>
+        <v>28.326</v>
       </c>
       <c r="J60">
-        <v>19.06444</v>
+        <v>19.06064</v>
       </c>
       <c r="K60">
-        <v>73.00342</v>
+        <v>72.99382</v>
       </c>
       <c r="L60" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M60" t="str">
         <v>Left</v>
       </c>
       <c r="N60" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="O60">
         <v>0</v>
@@ -4800,7 +4818,7 @@
         <v>0</v>
       </c>
       <c r="T60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U60">
         <v>0</v>
@@ -4812,7 +4830,7 @@
         <v>0</v>
       </c>
       <c r="Z60">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="AA60">
         <v>1</v>
@@ -4820,7 +4838,13 @@
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>H-2935</v>
+        <v>VSH S-5</v>
+      </c>
+      <c r="B61" t="str">
+        <v>VSH</v>
+      </c>
+      <c r="C61" t="str">
+        <v>Vashi</v>
       </c>
       <c r="D61" t="str">
         <v>CSMT-PNVL</v>
@@ -4832,28 +4856,28 @@
         <v>DN</v>
       </c>
       <c r="G61" t="str">
-        <v>29/H136</v>
+        <v>29/H102</v>
       </c>
       <c r="H61" t="str">
-        <v>29/H136</v>
+        <v>29/H102</v>
       </c>
       <c r="I61">
-        <v>29.8</v>
+        <v>29.044</v>
       </c>
       <c r="J61">
-        <v>19.06532</v>
+        <v>19.06359</v>
       </c>
       <c r="K61">
-        <v>73.00708</v>
+        <v>73.0002</v>
       </c>
       <c r="L61" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M61" t="str">
         <v>Left</v>
       </c>
       <c r="N61" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="O61">
         <v>0</v>
@@ -4874,7 +4898,7 @@
         <v>0</v>
       </c>
       <c r="U61">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V61">
         <v>0</v>
@@ -4883,7 +4907,7 @@
         <v>0</v>
       </c>
       <c r="Z61">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="AA61">
         <v>1</v>
@@ -4891,7 +4915,7 @@
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>H-3001</v>
+        <v>H-2921</v>
       </c>
       <c r="D62" t="str">
         <v>CSMT-PNVL</v>
@@ -4903,19 +4927,19 @@
         <v>DN</v>
       </c>
       <c r="G62" t="str">
-        <v>SNPD PF-3</v>
+        <v>29/H120</v>
       </c>
       <c r="H62" t="str">
-        <v>30/02</v>
+        <v>29/H120</v>
       </c>
       <c r="I62">
-        <v>30.23</v>
+        <v>29.402</v>
       </c>
       <c r="J62">
-        <v>19.06629</v>
+        <v>19.06444</v>
       </c>
       <c r="K62">
-        <v>73.01113</v>
+        <v>73.00342</v>
       </c>
       <c r="L62" t="str">
         <v>Automatic</v>
@@ -4954,7 +4978,7 @@
         <v>0</v>
       </c>
       <c r="Z62">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AA62">
         <v>1</v>
@@ -4962,7 +4986,7 @@
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>H-3013</v>
+        <v>H-2935</v>
       </c>
       <c r="D63" t="str">
         <v>CSMT-PNVL</v>
@@ -4974,19 +4998,19 @@
         <v>DN</v>
       </c>
       <c r="G63" t="str">
-        <v>30/H126</v>
+        <v>29/H136</v>
       </c>
       <c r="H63" t="str">
-        <v>30/H126</v>
+        <v>29/H136</v>
       </c>
       <c r="I63">
-        <v>30.719</v>
+        <v>29.8</v>
       </c>
       <c r="J63">
-        <v>19.06601</v>
+        <v>19.06532</v>
       </c>
       <c r="K63">
-        <v>73.01562</v>
+        <v>73.00708</v>
       </c>
       <c r="L63" t="str">
         <v>Automatic</v>
@@ -4995,7 +5019,7 @@
         <v>Left</v>
       </c>
       <c r="N63" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="O63">
         <v>0</v>
@@ -5025,7 +5049,7 @@
         <v>0</v>
       </c>
       <c r="Z63">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="AA63">
         <v>1</v>
@@ -5033,7 +5057,7 @@
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>H-3109</v>
+        <v>H-3001</v>
       </c>
       <c r="D64" t="str">
         <v>CSMT-PNVL</v>
@@ -5045,19 +5069,19 @@
         <v>DN</v>
       </c>
       <c r="G64" t="str">
-        <v>31/07</v>
+        <v>SNPD PF-3</v>
       </c>
       <c r="H64" t="str">
-        <v>31/07</v>
+        <v>30/02</v>
       </c>
       <c r="I64">
-        <v>31.238</v>
+        <v>30.23</v>
       </c>
       <c r="J64">
-        <v>19.06236</v>
+        <v>19.06629</v>
       </c>
       <c r="K64">
-        <v>73.01825</v>
+        <v>73.01113</v>
       </c>
       <c r="L64" t="str">
         <v>Automatic</v>
@@ -5066,7 +5090,7 @@
         <v>Left</v>
       </c>
       <c r="N64" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="O64">
         <v>0</v>
@@ -5096,7 +5120,7 @@
         <v>0</v>
       </c>
       <c r="Z64">
-        <v>250</v>
+        <v>700</v>
       </c>
       <c r="AA64">
         <v>1</v>
@@ -5104,7 +5128,7 @@
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>H-3141</v>
+        <v>H-3013</v>
       </c>
       <c r="D65" t="str">
         <v>CSMT-PNVL</v>
@@ -5116,19 +5140,19 @@
         <v>DN</v>
       </c>
       <c r="G65" t="str">
-        <v>31/17</v>
+        <v>30/H126</v>
       </c>
       <c r="H65" t="str">
-        <v>31/17</v>
+        <v>30/H126</v>
       </c>
       <c r="I65">
-        <v>31.663</v>
+        <v>30.719</v>
       </c>
       <c r="J65">
-        <v>19.05848</v>
+        <v>19.06601</v>
       </c>
       <c r="K65">
-        <v>73.01843</v>
+        <v>73.01562</v>
       </c>
       <c r="L65" t="str">
         <v>Automatic</v>
@@ -5137,7 +5161,7 @@
         <v>Left</v>
       </c>
       <c r="N65" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="O65">
         <v>0</v>
@@ -5167,7 +5191,7 @@
         <v>0</v>
       </c>
       <c r="Z65">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="AA65">
         <v>1</v>
@@ -5175,13 +5199,7 @@
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>JNJ S-4</v>
-      </c>
-      <c r="B66" t="str">
-        <v>JNJ</v>
-      </c>
-      <c r="C66" t="str">
-        <v>Juinagar</v>
+        <v>H-3109</v>
       </c>
       <c r="D66" t="str">
         <v>CSMT-PNVL</v>
@@ -5193,28 +5211,28 @@
         <v>DN</v>
       </c>
       <c r="G66" t="str">
-        <v>JNJ PF-3</v>
+        <v>31/07</v>
       </c>
       <c r="H66" t="str">
-        <v>32/01</v>
+        <v>31/07</v>
       </c>
       <c r="I66">
-        <v>32.096</v>
+        <v>31.238</v>
       </c>
       <c r="J66">
-        <v>19.05452</v>
+        <v>19.06236</v>
       </c>
       <c r="K66">
-        <v>73.01838</v>
+        <v>73.01825</v>
       </c>
       <c r="L66" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M66" t="str">
         <v>Left</v>
       </c>
       <c r="N66" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="O66">
         <v>0</v>
@@ -5229,7 +5247,7 @@
         <v>0</v>
       </c>
       <c r="S66">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T66">
         <v>0</v>
@@ -5244,7 +5262,7 @@
         <v>0</v>
       </c>
       <c r="Z66">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="AA66">
         <v>1</v>
@@ -5252,13 +5270,7 @@
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>JNJ S-6</v>
-      </c>
-      <c r="B67" t="str">
-        <v>JNJ</v>
-      </c>
-      <c r="C67" t="str">
-        <v>Juinagar</v>
+        <v>H-3141</v>
       </c>
       <c r="D67" t="str">
         <v>CSMT-PNVL</v>
@@ -5270,22 +5282,22 @@
         <v>DN</v>
       </c>
       <c r="G67" t="str">
-        <v>32/H122</v>
+        <v>31/17</v>
       </c>
       <c r="H67" t="str">
-        <v>32/H122</v>
+        <v>31/17</v>
       </c>
       <c r="I67">
-        <v>32.577</v>
+        <v>31.663</v>
       </c>
       <c r="J67">
-        <v>19.05026</v>
+        <v>19.05848</v>
       </c>
       <c r="K67">
-        <v>73.01886</v>
+        <v>73.01843</v>
       </c>
       <c r="L67" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M67" t="str">
         <v>Left</v>
@@ -5312,7 +5324,7 @@
         <v>0</v>
       </c>
       <c r="U67">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V67">
         <v>0</v>
@@ -5321,7 +5333,7 @@
         <v>0</v>
       </c>
       <c r="Z67">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="AA67">
         <v>1</v>
@@ -5329,7 +5341,7 @@
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>JNJ S-10</v>
+        <v>JNJ S-4</v>
       </c>
       <c r="B68" t="str">
         <v>JNJ</v>
@@ -5347,19 +5359,19 @@
         <v>DN</v>
       </c>
       <c r="G68" t="str">
-        <v>33/H104</v>
+        <v>JNJ PF-3</v>
       </c>
       <c r="H68" t="str">
-        <v>33/H104</v>
+        <v>32/01</v>
       </c>
       <c r="I68">
-        <v>33.079</v>
+        <v>32.096</v>
       </c>
       <c r="J68">
-        <v>19.04576</v>
+        <v>19.05452</v>
       </c>
       <c r="K68">
-        <v>73.01891</v>
+        <v>73.01838</v>
       </c>
       <c r="L68" t="str">
         <v>Semi-Automatic</v>
@@ -5398,7 +5410,7 @@
         <v>0</v>
       </c>
       <c r="Z68">
-        <v>600</v>
+        <v>350</v>
       </c>
       <c r="AA68">
         <v>1</v>
@@ -5406,13 +5418,13 @@
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>NEU S-4</v>
+        <v>JNJ S-6</v>
       </c>
       <c r="B69" t="str">
-        <v>NEU</v>
+        <v>JNJ</v>
       </c>
       <c r="C69" t="str">
-        <v>Nerul</v>
+        <v>Juinagar</v>
       </c>
       <c r="D69" t="str">
         <v>CSMT-PNVL</v>
@@ -5424,19 +5436,19 @@
         <v>DN</v>
       </c>
       <c r="G69" t="str">
-        <v>33/H134</v>
+        <v>32/H122</v>
       </c>
       <c r="H69" t="str">
-        <v>33/H134</v>
+        <v>32/H122</v>
       </c>
       <c r="I69">
-        <v>33.767</v>
+        <v>32.577</v>
       </c>
       <c r="J69">
-        <v>19.03944</v>
+        <v>19.05026</v>
       </c>
       <c r="K69">
-        <v>73.01867</v>
+        <v>73.01886</v>
       </c>
       <c r="L69" t="str">
         <v>Semi-Automatic</v>
@@ -5466,7 +5478,7 @@
         <v>0</v>
       </c>
       <c r="U69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V69">
         <v>0</v>
@@ -5475,7 +5487,7 @@
         <v>0</v>
       </c>
       <c r="Z69">
-        <v>600</v>
+        <v>300</v>
       </c>
       <c r="AA69">
         <v>1</v>
@@ -5483,13 +5495,13 @@
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>NEU S-33</v>
+        <v>JNJ S-10</v>
       </c>
       <c r="B70" t="str">
-        <v>NEU</v>
+        <v>JNJ</v>
       </c>
       <c r="C70" t="str">
-        <v>Nerul</v>
+        <v>Juinagar</v>
       </c>
       <c r="D70" t="str">
         <v>CSMT-PNVL</v>
@@ -5501,19 +5513,19 @@
         <v>DN</v>
       </c>
       <c r="G70" t="str">
-        <v>NEU PF-3</v>
+        <v>33/H104</v>
       </c>
       <c r="H70" t="str">
-        <v>34/07</v>
+        <v>33/H104</v>
       </c>
       <c r="I70">
-        <v>34.584</v>
+        <v>33.079</v>
       </c>
       <c r="J70">
-        <v>19.03224</v>
+        <v>19.04576</v>
       </c>
       <c r="K70">
-        <v>73.01819</v>
+        <v>73.01891</v>
       </c>
       <c r="L70" t="str">
         <v>Semi-Automatic</v>
@@ -5537,10 +5549,10 @@
         <v>0</v>
       </c>
       <c r="S70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T70">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U70">
         <v>0</v>
@@ -5549,16 +5561,10 @@
         <v>0</v>
       </c>
       <c r="W70">
-        <v>1</v>
-      </c>
-      <c r="X70" t="str">
-        <v>RI: R1=URAN</v>
-      </c>
-      <c r="Y70" t="str">
-        <v>Book shows one right arm on top of vertical stem</v>
+        <v>0</v>
       </c>
       <c r="Z70">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AA70">
         <v>1</v>
@@ -5566,7 +5572,7 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>NEU S-41</v>
+        <v>NEU S-4</v>
       </c>
       <c r="B71" t="str">
         <v>NEU</v>
@@ -5584,19 +5590,19 @@
         <v>DN</v>
       </c>
       <c r="G71" t="str">
-        <v>35/H110</v>
+        <v>33/H134</v>
       </c>
       <c r="H71" t="str">
-        <v>35/H110</v>
+        <v>33/H134</v>
       </c>
       <c r="I71">
-        <v>35.136</v>
+        <v>33.767</v>
       </c>
       <c r="J71">
-        <v>19.02751</v>
+        <v>19.03944</v>
       </c>
       <c r="K71">
-        <v>73.01684</v>
+        <v>73.01867</v>
       </c>
       <c r="L71" t="str">
         <v>Semi-Automatic</v>
@@ -5605,7 +5611,7 @@
         <v>Left</v>
       </c>
       <c r="N71" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="O71">
         <v>0</v>
@@ -5635,7 +5641,7 @@
         <v>0</v>
       </c>
       <c r="Z71">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="AA71">
         <v>1</v>
@@ -5643,7 +5649,13 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>H-3515</v>
+        <v>NEU S-33</v>
+      </c>
+      <c r="B72" t="str">
+        <v>NEU</v>
+      </c>
+      <c r="C72" t="str">
+        <v>Nerul</v>
       </c>
       <c r="D72" t="str">
         <v>CSMT-PNVL</v>
@@ -5655,28 +5667,28 @@
         <v>DN</v>
       </c>
       <c r="G72" t="str">
-        <v>35/H138</v>
+        <v>NEU PF-3</v>
       </c>
       <c r="H72" t="str">
-        <v>35/H138</v>
+        <v>34/07</v>
       </c>
       <c r="I72">
-        <v>35.537</v>
+        <v>34.584</v>
       </c>
       <c r="J72">
-        <v>19.024</v>
+        <v>19.03224</v>
       </c>
       <c r="K72">
-        <v>73.01729</v>
+        <v>73.01819</v>
       </c>
       <c r="L72" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M72" t="str">
         <v>Left</v>
       </c>
       <c r="N72" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="O72">
         <v>0</v>
@@ -5694,7 +5706,7 @@
         <v>0</v>
       </c>
       <c r="T72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U72">
         <v>0</v>
@@ -5703,10 +5715,16 @@
         <v>0</v>
       </c>
       <c r="W72">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X72" t="str">
+        <v>RI: R1=URAN</v>
+      </c>
+      <c r="Y72" t="str">
+        <v>Book shows one right arm on top of vertical stem</v>
       </c>
       <c r="Z72">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="AA72">
         <v>1</v>
@@ -5714,7 +5732,13 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>H-3601</v>
+        <v>NEU S-41</v>
+      </c>
+      <c r="B73" t="str">
+        <v>NEU</v>
+      </c>
+      <c r="C73" t="str">
+        <v>Nerul</v>
       </c>
       <c r="D73" t="str">
         <v>CSMT-PNVL</v>
@@ -5726,28 +5750,28 @@
         <v>DN</v>
       </c>
       <c r="G73" t="str">
-        <v>SEWD PF-1</v>
+        <v>35/H110</v>
       </c>
       <c r="H73" t="str">
-        <v>36/01</v>
+        <v>35/H110</v>
       </c>
       <c r="I73">
-        <v>36.005</v>
+        <v>35.136</v>
       </c>
       <c r="J73">
-        <v>19.02102</v>
+        <v>19.02751</v>
       </c>
       <c r="K73">
-        <v>73.02043</v>
+        <v>73.01684</v>
       </c>
       <c r="L73" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M73" t="str">
         <v>Left</v>
       </c>
       <c r="N73" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="O73">
         <v>0</v>
@@ -5785,7 +5809,7 @@
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>H-3607</v>
+        <v>H-3515</v>
       </c>
       <c r="D74" t="str">
         <v>CSMT-PNVL</v>
@@ -5797,19 +5821,19 @@
         <v>DN</v>
       </c>
       <c r="G74" t="str">
-        <v>36/H118</v>
+        <v>35/H138</v>
       </c>
       <c r="H74" t="str">
-        <v>36/H118</v>
+        <v>35/H138</v>
       </c>
       <c r="I74">
-        <v>36.782</v>
+        <v>35.537</v>
       </c>
       <c r="J74">
-        <v>19.01866</v>
+        <v>19.024</v>
       </c>
       <c r="K74">
-        <v>73.02306</v>
+        <v>73.01729</v>
       </c>
       <c r="L74" t="str">
         <v>Automatic</v>
@@ -5848,7 +5872,7 @@
         <v>0</v>
       </c>
       <c r="Z74">
-        <v>700</v>
+        <v>250</v>
       </c>
       <c r="AA74">
         <v>1</v>
@@ -5856,7 +5880,7 @@
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>H-3617</v>
+        <v>H-3601</v>
       </c>
       <c r="D75" t="str">
         <v>CSMT-PNVL</v>
@@ -5868,19 +5892,19 @@
         <v>DN</v>
       </c>
       <c r="G75" t="str">
-        <v>36/H138</v>
+        <v>SEWD PF-1</v>
       </c>
       <c r="H75" t="str">
-        <v>36/H138</v>
+        <v>36/01</v>
       </c>
       <c r="I75">
-        <v>37.156</v>
+        <v>36.005</v>
       </c>
       <c r="J75">
-        <v>19.01655</v>
+        <v>19.02102</v>
       </c>
       <c r="K75">
-        <v>73.02595</v>
+        <v>73.02043</v>
       </c>
       <c r="L75" t="str">
         <v>Automatic</v>
@@ -5919,7 +5943,7 @@
         <v>0</v>
       </c>
       <c r="Z75">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="AA75">
         <v>1</v>
@@ -5927,7 +5951,7 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>H-3703</v>
+        <v>H-3607</v>
       </c>
       <c r="D76" t="str">
         <v>CSMT-PNVL</v>
@@ -5939,19 +5963,19 @@
         <v>DN</v>
       </c>
       <c r="G76" t="str">
-        <v>37/H112</v>
+        <v>36/H118</v>
       </c>
       <c r="H76" t="str">
-        <v>37/H112</v>
+        <v>36/H118</v>
       </c>
       <c r="I76">
-        <v>37.568</v>
+        <v>36.782</v>
       </c>
       <c r="J76">
-        <v>19.01638</v>
+        <v>19.01866</v>
       </c>
       <c r="K76">
-        <v>73.02939</v>
+        <v>73.02306</v>
       </c>
       <c r="L76" t="str">
         <v>Automatic</v>
@@ -5960,7 +5984,7 @@
         <v>Left</v>
       </c>
       <c r="N76" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="O76">
         <v>0</v>
@@ -5990,7 +6014,7 @@
         <v>0</v>
       </c>
       <c r="Z76">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AA76">
         <v>1</v>
@@ -5998,13 +6022,7 @@
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>BEPR S-2</v>
-      </c>
-      <c r="B77" t="str">
-        <v>BEPR</v>
-      </c>
-      <c r="C77" t="str">
-        <v>Belapur</v>
+        <v>H-3617</v>
       </c>
       <c r="D77" t="str">
         <v>CSMT-PNVL</v>
@@ -6016,22 +6034,22 @@
         <v>DN</v>
       </c>
       <c r="G77" t="str">
-        <v>37/H128</v>
+        <v>36/H138</v>
       </c>
       <c r="H77" t="str">
-        <v>37/H128</v>
+        <v>36/H138</v>
       </c>
       <c r="I77">
-        <v>37.98</v>
+        <v>37.156</v>
       </c>
       <c r="J77">
-        <v>19.01686</v>
+        <v>19.01655</v>
       </c>
       <c r="K77">
-        <v>73.03325</v>
+        <v>73.02595</v>
       </c>
       <c r="L77" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M77" t="str">
         <v>Left</v>
@@ -6055,7 +6073,7 @@
         <v>0</v>
       </c>
       <c r="T77">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U77">
         <v>0</v>
@@ -6064,16 +6082,10 @@
         <v>0</v>
       </c>
       <c r="W77">
-        <v>1</v>
-      </c>
-      <c r="X77" t="str">
-        <v>RI: R1=PF-2</v>
-      </c>
-      <c r="Y77" t="str">
-        <v>Book shows one right arm on top of vertical stem</v>
+        <v>0</v>
       </c>
       <c r="Z77">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="AA77">
         <v>1</v>
@@ -6081,7 +6093,7 @@
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>H-3717 REP</v>
+        <v>H-3703</v>
       </c>
       <c r="D78" t="str">
         <v>CSMT-PNVL</v>
@@ -6093,25 +6105,28 @@
         <v>DN</v>
       </c>
       <c r="G78" t="str">
-        <v>37/16</v>
+        <v>37/H112</v>
       </c>
       <c r="H78" t="str">
-        <v>37/16</v>
+        <v>37/H112</v>
+      </c>
+      <c r="I78">
+        <v>37.568</v>
       </c>
       <c r="J78">
-        <v>19.01712</v>
+        <v>19.01638</v>
       </c>
       <c r="K78">
-        <v>73.03491</v>
+        <v>73.02939</v>
       </c>
       <c r="L78" t="str">
-        <v>Repeater</v>
+        <v>Automatic</v>
       </c>
       <c r="M78" t="str">
         <v>Left</v>
       </c>
       <c r="N78" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="O78">
         <v>0</v>
@@ -6141,7 +6156,7 @@
         <v>0</v>
       </c>
       <c r="Z78">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="AA78">
         <v>1</v>
@@ -6149,7 +6164,13 @@
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>H-3717</v>
+        <v>BEPR S-2</v>
+      </c>
+      <c r="B79" t="str">
+        <v>BEPR</v>
+      </c>
+      <c r="C79" t="str">
+        <v>Belapur</v>
       </c>
       <c r="D79" t="str">
         <v>CSMT-PNVL</v>
@@ -6161,28 +6182,28 @@
         <v>DN</v>
       </c>
       <c r="G79" t="str">
-        <v>37/H152</v>
+        <v>37/H128</v>
       </c>
       <c r="H79" t="str">
-        <v>37/H152</v>
+        <v>37/H128</v>
       </c>
       <c r="I79">
-        <v>38.386</v>
+        <v>37.98</v>
       </c>
       <c r="J79">
-        <v>19.01795</v>
+        <v>19.01686</v>
       </c>
       <c r="K79">
-        <v>73.03689</v>
+        <v>73.03325</v>
       </c>
       <c r="L79" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M79" t="str">
         <v>Left</v>
       </c>
       <c r="N79" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="O79">
         <v>0</v>
@@ -6197,10 +6218,10 @@
         <v>0</v>
       </c>
       <c r="S79">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U79">
         <v>0</v>
@@ -6209,27 +6230,24 @@
         <v>0</v>
       </c>
       <c r="W79">
-        <v>0</v>
+        <v>1</v>
+      </c>
+      <c r="X79" t="str">
+        <v>RI: R1=PF-2</v>
+      </c>
+      <c r="Y79" t="str">
+        <v>Book shows one right arm on top of vertical stem</v>
       </c>
       <c r="Z79">
-        <v>200</v>
+        <v>350</v>
       </c>
       <c r="AA79">
         <v>1</v>
-      </c>
-      <c r="AB79" t="str">
-        <v>Repeater</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>BEPR S-8</v>
-      </c>
-      <c r="B80" t="str">
-        <v>BEPR</v>
-      </c>
-      <c r="C80" t="str">
-        <v>Belapur</v>
+        <v>H-3717 REP</v>
       </c>
       <c r="D80" t="str">
         <v>CSMT-PNVL</v>
@@ -6241,28 +6259,25 @@
         <v>DN</v>
       </c>
       <c r="G80" t="str">
-        <v>BEPR PF-1</v>
+        <v>37/16</v>
       </c>
       <c r="H80" t="str">
-        <v>38/04</v>
-      </c>
-      <c r="I80">
-        <v>38.732</v>
+        <v>37/16</v>
       </c>
       <c r="J80">
-        <v>19.01994</v>
+        <v>19.01712</v>
       </c>
       <c r="K80">
-        <v>73.04016</v>
+        <v>73.03491</v>
       </c>
       <c r="L80" t="str">
-        <v>Semi-Automatic</v>
+        <v>Repeater</v>
       </c>
       <c r="M80" t="str">
         <v>Left</v>
       </c>
       <c r="N80" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="O80">
         <v>0</v>
@@ -6283,7 +6298,7 @@
         <v>0</v>
       </c>
       <c r="U80">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V80">
         <v>0</v>
@@ -6292,7 +6307,7 @@
         <v>0</v>
       </c>
       <c r="Z80">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="AA80">
         <v>1</v>
@@ -6300,13 +6315,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>BEPR S-22</v>
-      </c>
-      <c r="B81" t="str">
-        <v>BEPR</v>
-      </c>
-      <c r="C81" t="str">
-        <v>Belapur</v>
+        <v>H-3717</v>
       </c>
       <c r="D81" t="str">
         <v>CSMT-PNVL</v>
@@ -6318,28 +6327,28 @@
         <v>DN</v>
       </c>
       <c r="G81" t="str">
-        <v>38/H122</v>
+        <v>37/H152</v>
       </c>
       <c r="H81" t="str">
-        <v>38/H122</v>
+        <v>37/H152</v>
       </c>
       <c r="I81">
-        <v>39.205</v>
+        <v>38.386</v>
       </c>
       <c r="J81">
-        <v>19.02179</v>
+        <v>19.01795</v>
       </c>
       <c r="K81">
-        <v>73.04324</v>
+        <v>73.03689</v>
       </c>
       <c r="L81" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M81" t="str">
         <v>Left</v>
       </c>
       <c r="N81" t="str">
-        <v>Right</v>
+        <v>Left</v>
       </c>
       <c r="O81">
         <v>0</v>
@@ -6354,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="S81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T81">
         <v>0</v>
@@ -6369,15 +6378,24 @@
         <v>0</v>
       </c>
       <c r="Z81">
-        <v>800</v>
+        <v>200</v>
       </c>
       <c r="AA81">
         <v>1</v>
+      </c>
+      <c r="AB81" t="str">
+        <v>Repeater</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>H-3907</v>
+        <v>BEPR S-8</v>
+      </c>
+      <c r="B82" t="str">
+        <v>BEPR</v>
+      </c>
+      <c r="C82" t="str">
+        <v>Belapur</v>
       </c>
       <c r="D82" t="str">
         <v>CSMT-PNVL</v>
@@ -6389,28 +6407,28 @@
         <v>DN</v>
       </c>
       <c r="G82" t="str">
-        <v>39/H106</v>
+        <v>BEPR PF-1</v>
       </c>
       <c r="H82" t="str">
-        <v>39/H106</v>
+        <v>38/04</v>
       </c>
       <c r="I82">
-        <v>39.706</v>
+        <v>38.732</v>
       </c>
       <c r="J82">
-        <v>19.02197</v>
+        <v>19.01994</v>
       </c>
       <c r="K82">
-        <v>73.04712</v>
+        <v>73.04016</v>
       </c>
       <c r="L82" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M82" t="str">
         <v>Left</v>
       </c>
       <c r="N82" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="O82">
         <v>0</v>
@@ -6431,7 +6449,7 @@
         <v>0</v>
       </c>
       <c r="U82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V82">
         <v>0</v>
@@ -6448,7 +6466,13 @@
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>H-3917</v>
+        <v>BEPR S-22</v>
+      </c>
+      <c r="B83" t="str">
+        <v>BEPR</v>
+      </c>
+      <c r="C83" t="str">
+        <v>Belapur</v>
       </c>
       <c r="D83" t="str">
         <v>CSMT-PNVL</v>
@@ -6460,28 +6484,28 @@
         <v>DN</v>
       </c>
       <c r="G83" t="str">
-        <v>39/H124</v>
+        <v>38/H122</v>
       </c>
       <c r="H83" t="str">
-        <v>39/H124</v>
+        <v>38/H122</v>
       </c>
       <c r="I83">
-        <v>40.306</v>
+        <v>39.205</v>
       </c>
       <c r="J83">
-        <v>19.02181</v>
+        <v>19.02179</v>
       </c>
       <c r="K83">
-        <v>73.05078</v>
+        <v>73.04324</v>
       </c>
       <c r="L83" t="str">
-        <v>Automatic</v>
+        <v>Semi-Automatic</v>
       </c>
       <c r="M83" t="str">
         <v>Left</v>
       </c>
       <c r="N83" t="str">
-        <v>Left</v>
+        <v>Right</v>
       </c>
       <c r="O83">
         <v>0</v>
@@ -6511,7 +6535,7 @@
         <v>0</v>
       </c>
       <c r="Z83">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="AA83">
         <v>1</v>
@@ -6519,7 +6543,7 @@
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>H-4005</v>
+        <v>H-3907</v>
       </c>
       <c r="D84" t="str">
         <v>CSMT-PNVL</v>
@@ -6531,19 +6555,19 @@
         <v>DN</v>
       </c>
       <c r="G84" t="str">
-        <v>40/H110</v>
+        <v>39/H106</v>
       </c>
       <c r="H84" t="str">
-        <v>40/H110</v>
+        <v>39/H106</v>
       </c>
       <c r="I84">
-        <v>40.729</v>
+        <v>39.706</v>
       </c>
       <c r="J84">
-        <v>19.02478</v>
+        <v>19.02197</v>
       </c>
       <c r="K84">
-        <v>73.05685</v>
+        <v>73.04712</v>
       </c>
       <c r="L84" t="str">
         <v>Automatic</v>
@@ -6552,7 +6576,7 @@
         <v>Left</v>
       </c>
       <c r="N84" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="O84">
         <v>0</v>
@@ -6590,7 +6614,7 @@
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>H-4013</v>
+        <v>H-3917</v>
       </c>
       <c r="D85" t="str">
         <v>CSMT-PNVL</v>
@@ -6602,19 +6626,19 @@
         <v>DN</v>
       </c>
       <c r="G85" t="str">
-        <v>KHAG PF-1</v>
+        <v>39/H124</v>
       </c>
       <c r="H85" t="str">
-        <v>40/12</v>
+        <v>39/H124</v>
       </c>
       <c r="I85">
-        <v>41.138</v>
+        <v>40.306</v>
       </c>
       <c r="J85">
-        <v>19.02668</v>
+        <v>19.02181</v>
       </c>
       <c r="K85">
-        <v>73.06041</v>
+        <v>73.05078</v>
       </c>
       <c r="L85" t="str">
         <v>Automatic</v>
@@ -6623,7 +6647,7 @@
         <v>Left</v>
       </c>
       <c r="N85" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="O85">
         <v>0</v>
@@ -6653,7 +6677,7 @@
         <v>0</v>
       </c>
       <c r="Z85">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="AA85">
         <v>1</v>
@@ -6661,7 +6685,7 @@
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>H-4103</v>
+        <v>H-4005</v>
       </c>
       <c r="D86" t="str">
         <v>CSMT-PNVL</v>
@@ -6673,19 +6697,19 @@
         <v>DN</v>
       </c>
       <c r="G86" t="str">
-        <v>41/H106</v>
+        <v>40/H110</v>
       </c>
       <c r="H86" t="str">
-        <v>41/H106</v>
+        <v>40/H110</v>
       </c>
       <c r="I86">
-        <v>41.537</v>
+        <v>40.729</v>
       </c>
       <c r="J86">
-        <v>19.02843</v>
+        <v>19.02478</v>
       </c>
       <c r="K86">
-        <v>73.06387</v>
+        <v>73.05685</v>
       </c>
       <c r="L86" t="str">
         <v>Automatic</v>
@@ -6694,7 +6718,7 @@
         <v>Left</v>
       </c>
       <c r="N86" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="O86">
         <v>0</v>
@@ -6724,7 +6748,7 @@
         <v>0</v>
       </c>
       <c r="Z86">
-        <v>1000</v>
+        <v>400</v>
       </c>
       <c r="AA86">
         <v>1</v>
@@ -6732,7 +6756,7 @@
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>H-4115</v>
+        <v>H-4013</v>
       </c>
       <c r="D87" t="str">
         <v>CSMT-PNVL</v>
@@ -6744,19 +6768,19 @@
         <v>DN</v>
       </c>
       <c r="G87" t="str">
-        <v>41/H126</v>
+        <v>KHAG PF-1</v>
       </c>
       <c r="H87" t="str">
-        <v>41/H126</v>
+        <v>40/12</v>
       </c>
       <c r="I87">
-        <v>41.981</v>
+        <v>41.138</v>
       </c>
       <c r="J87">
-        <v>19.02865</v>
+        <v>19.02668</v>
       </c>
       <c r="K87">
-        <v>73.06754</v>
+        <v>73.06041</v>
       </c>
       <c r="L87" t="str">
         <v>Automatic</v>
@@ -6765,7 +6789,7 @@
         <v>Left</v>
       </c>
       <c r="N87" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="O87">
         <v>0</v>
@@ -6795,7 +6819,7 @@
         <v>0</v>
       </c>
       <c r="Z87">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="AA87">
         <v>1</v>
@@ -6803,7 +6827,7 @@
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>H-4201</v>
+        <v>H-4103</v>
       </c>
       <c r="D88" t="str">
         <v>CSMT-PNVL</v>
@@ -6815,19 +6839,19 @@
         <v>DN</v>
       </c>
       <c r="G88" t="str">
-        <v>41/H148</v>
+        <v>41/H106</v>
       </c>
       <c r="H88" t="str">
-        <v>41/H148</v>
+        <v>41/H106</v>
       </c>
       <c r="I88">
-        <v>42.567</v>
+        <v>41.537</v>
       </c>
       <c r="J88">
-        <v>19.02648</v>
+        <v>19.02843</v>
       </c>
       <c r="K88">
-        <v>73.07089</v>
+        <v>73.06387</v>
       </c>
       <c r="L88" t="str">
         <v>Automatic</v>
@@ -6866,7 +6890,7 @@
         <v>0</v>
       </c>
       <c r="Z88">
-        <v>400</v>
+        <v>1000</v>
       </c>
       <c r="AA88">
         <v>1</v>
@@ -6874,7 +6898,7 @@
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>H-4211</v>
+        <v>H-4115</v>
       </c>
       <c r="D89" t="str">
         <v>CSMT-PNVL</v>
@@ -6886,19 +6910,19 @@
         <v>DN</v>
       </c>
       <c r="G89" t="str">
-        <v>42/H118</v>
+        <v>41/H126</v>
       </c>
       <c r="H89" t="str">
-        <v>42/H118</v>
+        <v>41/H126</v>
       </c>
       <c r="I89">
-        <v>43.125</v>
+        <v>41.981</v>
       </c>
       <c r="J89">
-        <v>19.02253</v>
+        <v>19.02865</v>
       </c>
       <c r="K89">
-        <v>73.07482</v>
+        <v>73.06754</v>
       </c>
       <c r="L89" t="str">
         <v>Automatic</v>
@@ -6907,7 +6931,7 @@
         <v>Left</v>
       </c>
       <c r="N89" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="O89">
         <v>0</v>
@@ -6937,7 +6961,7 @@
         <v>0</v>
       </c>
       <c r="Z89">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AA89">
         <v>1</v>
@@ -6945,7 +6969,7 @@
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>H-4301</v>
+        <v>H-4201</v>
       </c>
       <c r="D90" t="str">
         <v>CSMT-PNVL</v>
@@ -6957,19 +6981,19 @@
         <v>DN</v>
       </c>
       <c r="G90" t="str">
-        <v>43/H102</v>
+        <v>41/H148</v>
       </c>
       <c r="H90" t="str">
-        <v>43/H102</v>
+        <v>41/H148</v>
       </c>
       <c r="I90">
-        <v>43.638</v>
+        <v>42.567</v>
       </c>
       <c r="J90">
-        <v>19.01887</v>
+        <v>19.02648</v>
       </c>
       <c r="K90">
-        <v>73.07843</v>
+        <v>73.07089</v>
       </c>
       <c r="L90" t="str">
         <v>Automatic</v>
@@ -6978,7 +7002,7 @@
         <v>Left</v>
       </c>
       <c r="N90" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="O90">
         <v>0</v>
@@ -7016,7 +7040,7 @@
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>H-4311</v>
+        <v>H-4211</v>
       </c>
       <c r="D91" t="str">
         <v>CSMT-PNVL</v>
@@ -7028,19 +7052,19 @@
         <v>DN</v>
       </c>
       <c r="G91" t="str">
-        <v>MANR PF-1</v>
+        <v>42/H118</v>
       </c>
       <c r="H91" t="str">
-        <v>43/11</v>
+        <v>42/H118</v>
       </c>
       <c r="I91">
-        <v>44.017</v>
+        <v>43.125</v>
       </c>
       <c r="J91">
-        <v>19.0155</v>
+        <v>19.02253</v>
       </c>
       <c r="K91">
-        <v>73.08178</v>
+        <v>73.07482</v>
       </c>
       <c r="L91" t="str">
         <v>Automatic</v>
@@ -7087,7 +7111,7 @@
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>H-4401</v>
+        <v>H-4301</v>
       </c>
       <c r="D92" t="str">
         <v>CSMT-PNVL</v>
@@ -7099,19 +7123,19 @@
         <v>DN</v>
       </c>
       <c r="G92" t="str">
-        <v>43/17</v>
+        <v>43/H102</v>
       </c>
       <c r="H92" t="str">
-        <v>43/17</v>
+        <v>43/H102</v>
       </c>
       <c r="I92">
-        <v>44.417</v>
+        <v>43.638</v>
       </c>
       <c r="J92">
-        <v>19.01301</v>
+        <v>19.01887</v>
       </c>
       <c r="K92">
-        <v>73.08424</v>
+        <v>73.07843</v>
       </c>
       <c r="L92" t="str">
         <v>Automatic</v>
@@ -7150,7 +7174,7 @@
         <v>0</v>
       </c>
       <c r="Z92">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="AA92">
         <v>1</v>
@@ -7158,7 +7182,7 @@
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>H-4409</v>
+        <v>H-4311</v>
       </c>
       <c r="D93" t="str">
         <v>CSMT-PNVL</v>
@@ -7170,19 +7194,19 @@
         <v>DN</v>
       </c>
       <c r="G93" t="str">
-        <v>44/H114</v>
+        <v>MANR PF-1</v>
       </c>
       <c r="H93" t="str">
-        <v>44/H114</v>
+        <v>43/11</v>
       </c>
       <c r="I93">
-        <v>44.98</v>
+        <v>44.017</v>
       </c>
       <c r="J93">
-        <v>19.01042</v>
+        <v>19.0155</v>
       </c>
       <c r="K93">
-        <v>73.08682</v>
+        <v>73.08178</v>
       </c>
       <c r="L93" t="str">
         <v>Automatic</v>
@@ -7191,7 +7215,7 @@
         <v>Left</v>
       </c>
       <c r="N93" t="str">
-        <v>Left</v>
+        <v>Unknown</v>
       </c>
       <c r="O93">
         <v>0</v>
@@ -7221,7 +7245,7 @@
         <v>0</v>
       </c>
       <c r="Z93">
-        <v>400</v>
+        <v>700</v>
       </c>
       <c r="AA93">
         <v>1</v>
@@ -7229,7 +7253,7 @@
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>H-4421</v>
+        <v>H-4401</v>
       </c>
       <c r="D94" t="str">
         <v>CSMT-PNVL</v>
@@ -7241,19 +7265,19 @@
         <v>DN</v>
       </c>
       <c r="G94" t="str">
-        <v>44/H140</v>
+        <v>43/17</v>
       </c>
       <c r="H94" t="str">
-        <v>44/H140</v>
+        <v>43/17</v>
       </c>
       <c r="I94">
-        <v>45.54</v>
+        <v>44.417</v>
       </c>
       <c r="J94">
-        <v>19.00833</v>
+        <v>19.01301</v>
       </c>
       <c r="K94">
-        <v>73.09155</v>
+        <v>73.08424</v>
       </c>
       <c r="L94" t="str">
         <v>Automatic</v>
@@ -7292,7 +7316,7 @@
         <v>0</v>
       </c>
       <c r="Z94">
-        <v>300</v>
+        <v>600</v>
       </c>
       <c r="AA94">
         <v>1</v>
@@ -7300,7 +7324,7 @@
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>H-4509</v>
+        <v>H-4409</v>
       </c>
       <c r="D95" t="str">
         <v>CSMT-PNVL</v>
@@ -7312,19 +7336,19 @@
         <v>DN</v>
       </c>
       <c r="G95" t="str">
-        <v>KNDS PF-1</v>
+        <v>44/H114</v>
       </c>
       <c r="H95" t="str">
-        <v>45/09</v>
+        <v>44/H114</v>
       </c>
       <c r="I95">
-        <v>45.94</v>
+        <v>44.98</v>
       </c>
       <c r="J95">
-        <v>19.00713</v>
+        <v>19.01042</v>
       </c>
       <c r="K95">
-        <v>73.09675</v>
+        <v>73.08682</v>
       </c>
       <c r="L95" t="str">
         <v>Automatic</v>
@@ -7333,7 +7357,7 @@
         <v>Left</v>
       </c>
       <c r="N95" t="str">
-        <v>Unknown</v>
+        <v>Left</v>
       </c>
       <c r="O95">
         <v>0</v>
@@ -7363,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="Z95">
-        <v>350</v>
+        <v>400</v>
       </c>
       <c r="AA95">
         <v>1</v>
@@ -7371,7 +7395,7 @@
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>H-4517</v>
+        <v>H-4421</v>
       </c>
       <c r="D96" t="str">
         <v>CSMT-PNVL</v>
@@ -7383,19 +7407,19 @@
         <v>DN</v>
       </c>
       <c r="G96" t="str">
-        <v>45/H140</v>
+        <v>44/H140</v>
       </c>
       <c r="H96" t="str">
-        <v>45/H140</v>
+        <v>44/H140</v>
       </c>
       <c r="I96">
-        <v>46.333</v>
+        <v>45.54</v>
       </c>
       <c r="J96">
-        <v>19.00625</v>
+        <v>19.00833</v>
       </c>
       <c r="K96">
-        <v>73.1004</v>
+        <v>73.09155</v>
       </c>
       <c r="L96" t="str">
         <v>Automatic</v>
@@ -7434,7 +7458,7 @@
         <v>0</v>
       </c>
       <c r="Z96">
-        <v>800</v>
+        <v>300</v>
       </c>
       <c r="AA96">
         <v>1</v>
@@ -7442,7 +7466,7 @@
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>H-4607</v>
+        <v>H-4509</v>
       </c>
       <c r="D97" t="str">
         <v>CSMT-PNVL</v>
@@ -7454,19 +7478,19 @@
         <v>DN</v>
       </c>
       <c r="G97" t="str">
-        <v>46/H112</v>
+        <v>KNDS PF-1</v>
       </c>
       <c r="H97" t="str">
-        <v>46/H112</v>
+        <v>45/09</v>
       </c>
       <c r="I97">
-        <v>46.768</v>
+        <v>45.94</v>
       </c>
       <c r="J97">
-        <v>19.00474</v>
+        <v>19.00713</v>
       </c>
       <c r="K97">
-        <v>73.10375</v>
+        <v>73.09675</v>
       </c>
       <c r="L97" t="str">
         <v>Automatic</v>
@@ -7475,7 +7499,7 @@
         <v>Left</v>
       </c>
       <c r="N97" t="str">
-        <v>Right</v>
+        <v>Unknown</v>
       </c>
       <c r="O97">
         <v>0</v>
@@ -7505,7 +7529,7 @@
         <v>0</v>
       </c>
       <c r="Z97">
-        <v>400</v>
+        <v>350</v>
       </c>
       <c r="AA97">
         <v>1</v>
@@ -7513,7 +7537,7 @@
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>H-4615</v>
+        <v>H-4517</v>
       </c>
       <c r="D98" t="str">
         <v>CSMT-PNVL</v>
@@ -7525,19 +7549,19 @@
         <v>DN</v>
       </c>
       <c r="G98" t="str">
-        <v>46/H132</v>
+        <v>45/H140</v>
       </c>
       <c r="H98" t="str">
-        <v>46/H132</v>
+        <v>45/H140</v>
       </c>
       <c r="I98">
-        <v>47.141</v>
+        <v>46.333</v>
       </c>
       <c r="J98">
-        <v>19.00278</v>
+        <v>19.00625</v>
       </c>
       <c r="K98">
-        <v>73.10733</v>
+        <v>73.1004</v>
       </c>
       <c r="L98" t="str">
         <v>Automatic</v>
@@ -7576,7 +7600,7 @@
         <v>0</v>
       </c>
       <c r="Z98">
-        <v>700</v>
+        <v>800</v>
       </c>
       <c r="AA98">
         <v>1</v>
@@ -7584,7 +7608,7 @@
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>H-4703</v>
+        <v>H-4607</v>
       </c>
       <c r="D99" t="str">
         <v>CSMT-PNVL</v>
@@ -7596,19 +7620,19 @@
         <v>DN</v>
       </c>
       <c r="G99" t="str">
-        <v>47/H104</v>
+        <v>46/H112</v>
       </c>
       <c r="H99" t="str">
-        <v>47/H104</v>
+        <v>46/H112</v>
       </c>
       <c r="I99">
-        <v>47.669</v>
+        <v>46.768</v>
       </c>
       <c r="J99">
-        <v>19.00113</v>
+        <v>19.00474</v>
       </c>
       <c r="K99">
-        <v>73.11038</v>
+        <v>73.10375</v>
       </c>
       <c r="L99" t="str">
         <v>Automatic</v>
@@ -7617,7 +7641,7 @@
         <v>Left</v>
       </c>
       <c r="N99" t="str">
-        <v>Unknown</v>
+        <v>Right</v>
       </c>
       <c r="O99">
         <v>0</v>
@@ -7647,7 +7671,7 @@
         <v>0</v>
       </c>
       <c r="Z99">
-        <v>700</v>
+        <v>400</v>
       </c>
       <c r="AA99">
         <v>1</v>
@@ -7655,13 +7679,7 @@
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>PNVL S-402</v>
-      </c>
-      <c r="B100" t="str">
-        <v>PNVL</v>
-      </c>
-      <c r="C100" t="str">
-        <v>Panvel</v>
+        <v>H-4615</v>
       </c>
       <c r="D100" t="str">
         <v>CSMT-PNVL</v>
@@ -7673,22 +7691,22 @@
         <v>DN</v>
       </c>
       <c r="G100" t="str">
-        <v>47/H136</v>
+        <v>46/H132</v>
       </c>
       <c r="H100" t="str">
-        <v>47/H136</v>
+        <v>46/H132</v>
       </c>
       <c r="I100">
-        <v>48.181</v>
+        <v>47.141</v>
       </c>
       <c r="J100">
-        <v>18.99785</v>
+        <v>19.00278</v>
       </c>
       <c r="K100">
-        <v>73.11405</v>
+        <v>73.10733</v>
       </c>
       <c r="L100" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M100" t="str">
         <v>Left</v>
@@ -7712,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="T100">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U100">
         <v>0</v>
@@ -7721,16 +7739,10 @@
         <v>0</v>
       </c>
       <c r="W100">
-        <v>1</v>
-      </c>
-      <c r="X100" t="str">
-        <v>RI: R1=S-404</v>
-      </c>
-      <c r="Y100" t="str">
-        <v>Book shows one right arm on top of vertical stem</v>
+        <v>0</v>
       </c>
       <c r="Z100">
-        <v>300</v>
+        <v>700</v>
       </c>
       <c r="AA100">
         <v>1</v>
@@ -7738,13 +7750,7 @@
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>PNVL S-403</v>
-      </c>
-      <c r="B101" t="str">
-        <v>PNVL</v>
-      </c>
-      <c r="C101" t="str">
-        <v>Panvel</v>
+        <v>H-4703</v>
       </c>
       <c r="D101" t="str">
         <v>CSMT-PNVL</v>
@@ -7756,22 +7762,22 @@
         <v>DN</v>
       </c>
       <c r="G101" t="str">
-        <v>48/H110</v>
+        <v>47/H104</v>
       </c>
       <c r="H101" t="str">
-        <v>48/H110</v>
+        <v>47/H104</v>
       </c>
       <c r="I101">
-        <v>48.815</v>
+        <v>47.669</v>
       </c>
       <c r="J101">
-        <v>18.99453</v>
+        <v>19.00113</v>
       </c>
       <c r="K101">
-        <v>73.11724</v>
+        <v>73.11038</v>
       </c>
       <c r="L101" t="str">
-        <v>Semi-Automatic</v>
+        <v>Automatic</v>
       </c>
       <c r="M101" t="str">
         <v>Left</v>
@@ -7795,33 +7801,193 @@
         <v>0</v>
       </c>
       <c r="T101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V101">
         <v>0</v>
       </c>
       <c r="W101">
-        <v>1</v>
-      </c>
-      <c r="X101" t="str">
+        <v>0</v>
+      </c>
+      <c r="Z101">
+        <v>700</v>
+      </c>
+      <c r="AA101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>PNVL S-402</v>
+      </c>
+      <c r="B102" t="str">
+        <v>PNVL</v>
+      </c>
+      <c r="C102" t="str">
+        <v>Panvel</v>
+      </c>
+      <c r="D102" t="str">
+        <v>CSMT-PNVL</v>
+      </c>
+      <c r="E102" t="str">
+        <v>DN HB</v>
+      </c>
+      <c r="F102" t="str">
+        <v>DN</v>
+      </c>
+      <c r="G102" t="str">
+        <v>47/H136</v>
+      </c>
+      <c r="H102" t="str">
+        <v>47/H136</v>
+      </c>
+      <c r="I102">
+        <v>48.181</v>
+      </c>
+      <c r="J102">
+        <v>18.99785</v>
+      </c>
+      <c r="K102">
+        <v>73.11405</v>
+      </c>
+      <c r="L102" t="str">
+        <v>Semi-Automatic</v>
+      </c>
+      <c r="M102" t="str">
+        <v>Left</v>
+      </c>
+      <c r="N102" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O102">
+        <v>0</v>
+      </c>
+      <c r="P102">
+        <v>0</v>
+      </c>
+      <c r="Q102">
+        <v>1</v>
+      </c>
+      <c r="R102">
+        <v>0</v>
+      </c>
+      <c r="S102">
+        <v>0</v>
+      </c>
+      <c r="T102">
+        <v>1</v>
+      </c>
+      <c r="U102">
+        <v>0</v>
+      </c>
+      <c r="V102">
+        <v>0</v>
+      </c>
+      <c r="W102">
+        <v>1</v>
+      </c>
+      <c r="X102" t="str">
+        <v>RI: R1=S-404</v>
+      </c>
+      <c r="Y102" t="str">
+        <v>Book shows one right arm on top of vertical stem</v>
+      </c>
+      <c r="Z102">
+        <v>300</v>
+      </c>
+      <c r="AA102">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>PNVL S-403</v>
+      </c>
+      <c r="B103" t="str">
+        <v>PNVL</v>
+      </c>
+      <c r="C103" t="str">
+        <v>Panvel</v>
+      </c>
+      <c r="D103" t="str">
+        <v>CSMT-PNVL</v>
+      </c>
+      <c r="E103" t="str">
+        <v>DN HB</v>
+      </c>
+      <c r="F103" t="str">
+        <v>DN</v>
+      </c>
+      <c r="G103" t="str">
+        <v>48/H110</v>
+      </c>
+      <c r="H103" t="str">
+        <v>48/H110</v>
+      </c>
+      <c r="I103">
+        <v>48.815</v>
+      </c>
+      <c r="J103">
+        <v>18.99453</v>
+      </c>
+      <c r="K103">
+        <v>73.11724</v>
+      </c>
+      <c r="L103" t="str">
+        <v>Semi-Automatic</v>
+      </c>
+      <c r="M103" t="str">
+        <v>Left</v>
+      </c>
+      <c r="N103" t="str">
+        <v>Unknown</v>
+      </c>
+      <c r="O103">
+        <v>0</v>
+      </c>
+      <c r="P103">
+        <v>0</v>
+      </c>
+      <c r="Q103">
+        <v>1</v>
+      </c>
+      <c r="R103">
+        <v>0</v>
+      </c>
+      <c r="S103">
+        <v>0</v>
+      </c>
+      <c r="T103">
+        <v>1</v>
+      </c>
+      <c r="U103">
+        <v>1</v>
+      </c>
+      <c r="V103">
+        <v>0</v>
+      </c>
+      <c r="W103">
+        <v>1</v>
+      </c>
+      <c r="X103" t="str">
         <v>RI: R1=PF-2</v>
       </c>
-      <c r="Y101" t="str">
+      <c r="Y103" t="str">
         <v>Book shows one right arm on top of vertical stem</v>
       </c>
-      <c r="Z101">
+      <c r="Z103">
         <v>500</v>
       </c>
-      <c r="AA101">
+      <c r="AA103">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AB101"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AB103"/>
   </ignoredErrors>
 </worksheet>
 </file>